--- a/projects/2026-05-fujie-gcard-v1/versions/fujie_gcard_v7_20260630/reports/model_report.xlsx
+++ b/projects/2026-05-fujie-gcard-v1/versions/fujie_gcard_v7_20260630/reports/model_report.xlsx
@@ -1145,7 +1145,7 @@
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>更新日期：2026-06-30；指标来源：当前 run 已注册 train/evaluation artifacts。</t>
+          <t>更新日期：2026-07-01；指标来源：当前 run 已注册 train/evaluation artifacts。</t>
         </is>
       </c>
     </row>
@@ -6490,7 +6490,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>

--- a/projects/2026-05-fujie-gcard-v1/versions/fujie_gcard_v7_20260630/reports/model_report.xlsx
+++ b/projects/2026-05-fujie-gcard-v1/versions/fujie_gcard_v7_20260630/reports/model_report.xlsx
@@ -1145,7 +1145,7 @@
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>更新日期：2026-07-01；指标来源：当前 run 已注册 train/evaluation artifacts。</t>
+          <t>更新日期：2026-07-02；指标来源：当前 run 已注册 train/evaluation artifacts。</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>本轮 model_score vs 旧版全客群 G卡V6</t>
+          <t>G卡V7 model_score vs 旧版全客群 G卡V6</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>本轮AUC</t>
+          <t>G卡V7 AUC</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
-          <t>本轮KS</t>
+          <t>G卡V7 KS</t>
         </is>
       </c>
       <c r="K67" s="6" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>本轮AUC</t>
+          <t>G卡V7 AUC</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="K77" s="6" t="inlineStr">
         <is>
-          <t>本轮KS</t>
+          <t>G卡V7 KS</t>
         </is>
       </c>
       <c r="L77" s="6" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>本轮AUC</t>
+          <t>G卡V7 AUC</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="K86" s="6" t="inlineStr">
         <is>
-          <t>本轮KS</t>
+          <t>G卡V7 KS</t>
         </is>
       </c>
       <c r="L86" s="6" t="inlineStr">
@@ -3012,7 +3012,7 @@
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>DEV-OOS 2025-06</t>
+          <t>2025-06 DEV-OOS</t>
         </is>
       </c>
       <c r="B87" s="8" t="n">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="H87" s="7" t="inlineStr">
         <is>
-          <t>DEV-OOS 2025-06</t>
+          <t>2025-06 DEV-OOS</t>
         </is>
       </c>
       <c r="I87" s="8" t="n">
@@ -3054,7 +3054,7 @@
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>DEV-OOS 2025-07</t>
+          <t>2025-07 DEV-OOS</t>
         </is>
       </c>
       <c r="B88" s="8" t="n">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="H88" s="7" t="inlineStr">
         <is>
-          <t>DEV-OOS 2025-07</t>
+          <t>2025-07 DEV-OOS</t>
         </is>
       </c>
       <c r="I88" s="8" t="n">
@@ -3096,7 +3096,7 @@
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>DEV-OOS 2025-08</t>
+          <t>2025-08 DEV-OOS</t>
         </is>
       </c>
       <c r="B89" s="8" t="n">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="H89" s="7" t="inlineStr">
         <is>
-          <t>DEV-OOS 2025-08</t>
+          <t>2025-08 DEV-OOS</t>
         </is>
       </c>
       <c r="I89" s="8" t="n">
@@ -3138,7 +3138,7 @@
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>DEV-OOS 2025-09</t>
+          <t>2025-09 DEV-OOS</t>
         </is>
       </c>
       <c r="B90" s="8" t="n">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="H90" s="7" t="inlineStr">
         <is>
-          <t>DEV-OOS 2025-09</t>
+          <t>2025-09 DEV-OOS</t>
         </is>
       </c>
       <c r="I90" s="8" t="n">
@@ -3180,7 +3180,7 @@
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>DEV-OOS 2025-10</t>
+          <t>2025-10 DEV-OOS</t>
         </is>
       </c>
       <c r="B91" s="8" t="n">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="H91" s="7" t="inlineStr">
         <is>
-          <t>DEV-OOS 2025-10</t>
+          <t>2025-10 DEV-OOS</t>
         </is>
       </c>
       <c r="I91" s="8" t="n">
@@ -3222,7 +3222,7 @@
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>DEV-OOS 2025-11</t>
+          <t>2025-11 DEV-OOS</t>
         </is>
       </c>
       <c r="B92" s="8" t="n">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="H92" s="7" t="inlineStr">
         <is>
-          <t>DEV-OOS 2025-11</t>
+          <t>2025-11 DEV-OOS</t>
         </is>
       </c>
       <c r="I92" s="8" t="n">
@@ -3264,7 +3264,7 @@
     <row r="93">
       <c r="A93" s="7" t="inlineStr">
         <is>
-          <t>OOT-OOS 2025-12</t>
+          <t>2025-12 OOT-OOS</t>
         </is>
       </c>
       <c r="B93" s="8" t="n">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="H93" s="7" t="inlineStr">
         <is>
-          <t>OOT-OOS 2025-12</t>
+          <t>2025-12 OOT-OOS</t>
         </is>
       </c>
       <c r="I93" s="8" t="n">
@@ -3306,7 +3306,7 @@
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>OOT-OOS 2026-01</t>
+          <t>2026-01 OOT-OOS</t>
         </is>
       </c>
       <c r="B94" s="8" t="n">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="H94" s="7" t="inlineStr">
         <is>
-          <t>OOT-OOS 2026-01</t>
+          <t>2026-01 OOT-OOS</t>
         </is>
       </c>
       <c r="I94" s="8" t="n">
@@ -3388,7 +3388,7 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>本轮模型</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="B103" s="5" t="n"/>
@@ -3475,8 +3475,10 @@
           <t>001</t>
         </is>
       </c>
-      <c r="B105" s="9" t="n">
-        <v>0.1000014293210929</v>
+      <c r="B105" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C105" s="9" t="n">
         <v>0.001184277692700357</v>
@@ -3495,8 +3497,10 @@
           <t>001</t>
         </is>
       </c>
-      <c r="I105" s="9" t="n">
-        <v>0.1000014293210929</v>
+      <c r="I105" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J105" s="9" t="n">
         <v>0.0007146503318019398</v>
@@ -3517,8 +3521,10 @@
           <t>002</t>
         </is>
       </c>
-      <c r="B106" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="B106" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C106" s="9" t="n">
         <v>0.00175601588581813</v>
@@ -3537,8 +3543,10 @@
           <t>002</t>
         </is>
       </c>
-      <c r="I106" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="I106" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J106" s="9" t="n">
         <v>0.001143452204718782</v>
@@ -3559,8 +3567,10 @@
           <t>003</t>
         </is>
       </c>
-      <c r="B107" s="9" t="n">
-        <v>0.1000014293210929</v>
+      <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C107" s="9" t="n">
         <v>0.002307315346709863</v>
@@ -3579,8 +3589,10 @@
           <t>003</t>
         </is>
       </c>
-      <c r="I107" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="I107" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J107" s="9" t="n">
         <v>0.001912566446369867</v>
@@ -3601,8 +3613,10 @@
           <t>004</t>
         </is>
       </c>
-      <c r="B108" s="9" t="n">
-        <v>0.09999734554654176</v>
+      <c r="B108" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C108" s="9" t="n">
         <v>0.003292546593362839</v>
@@ -3621,8 +3635,10 @@
           <t>004</t>
         </is>
       </c>
-      <c r="I108" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="I108" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J108" s="9" t="n">
         <v>0.002863749827715585</v>
@@ -3643,8 +3659,10 @@
           <t>005</t>
         </is>
       </c>
-      <c r="B109" s="9" t="n">
-        <v>0.1000014293210929</v>
+      <c r="B109" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C109" s="9" t="n">
         <v>0.004659577248521677</v>
@@ -3663,8 +3681,10 @@
           <t>005</t>
         </is>
       </c>
-      <c r="I109" s="9" t="n">
-        <v>0.1000014293210929</v>
+      <c r="I109" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J109" s="9" t="n">
         <v>0.004630990885033813</v>
@@ -3685,8 +3705,10 @@
           <t>006</t>
         </is>
       </c>
-      <c r="B110" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="B110" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C110" s="9" t="n">
         <v>0.008347910129795879</v>
@@ -3705,8 +3727,10 @@
           <t>006</t>
         </is>
       </c>
-      <c r="I110" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="I110" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J110" s="9" t="n">
         <v>0.008698433873525589</v>
@@ -3727,8 +3751,10 @@
           <t>007</t>
         </is>
       </c>
-      <c r="B111" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="B111" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C111" s="9" t="n">
         <v>0.01908581763024328</v>
@@ -3747,8 +3773,10 @@
           <t>007</t>
         </is>
       </c>
-      <c r="I111" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="I111" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J111" s="9" t="n">
         <v>0.01999883320693075</v>
@@ -3769,8 +3797,10 @@
           <t>008</t>
         </is>
       </c>
-      <c r="B112" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="B112" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C112" s="9" t="n">
         <v>0.04262444039469721</v>
@@ -3789,8 +3819,10 @@
           <t>008</t>
         </is>
       </c>
-      <c r="I112" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="I112" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J112" s="9" t="n">
         <v>0.04469185337192504</v>
@@ -3811,8 +3843,10 @@
           <t>009</t>
         </is>
       </c>
-      <c r="B113" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="B113" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C113" s="9" t="n">
         <v>0.08662607085813852</v>
@@ -3831,8 +3865,10 @@
           <t>009</t>
         </is>
       </c>
-      <c r="I113" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="I113" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J113" s="9" t="n">
         <v>0.0883344525918397</v>
@@ -3853,8 +3889,10 @@
           <t>010</t>
         </is>
       </c>
-      <c r="B114" s="9" t="n">
-        <v>0.1000014293210929</v>
+      <c r="B114" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C114" s="9" t="n">
         <v>0.1567332253855594</v>
@@ -3873,8 +3911,10 @@
           <t>010</t>
         </is>
       </c>
-      <c r="I114" s="9" t="n">
-        <v>0.1000014293210929</v>
+      <c r="I114" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J114" s="9" t="n">
         <v>0.1567332253855594</v>
@@ -3909,7 +3949,7 @@
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>本轮模型</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="B119" s="5" t="n"/>
@@ -3996,8 +4036,10 @@
           <t>001</t>
         </is>
       </c>
-      <c r="B121" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B121" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C121" s="9" t="n">
         <v>0.06459948320413436</v>
@@ -4016,8 +4058,10 @@
           <t>001</t>
         </is>
       </c>
-      <c r="I121" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="I121" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J121" s="9" t="n">
         <v>0.06921373200442968</v>
@@ -4038,8 +4082,10 @@
           <t>002</t>
         </is>
       </c>
-      <c r="B122" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B122" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C122" s="9" t="n">
         <v>0.09246954595791805</v>
@@ -4058,8 +4104,10 @@
           <t>002</t>
         </is>
       </c>
-      <c r="I122" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="I122" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J122" s="9" t="n">
         <v>0.09972929740371601</v>
@@ -4080,8 +4128,10 @@
           <t>003</t>
         </is>
       </c>
-      <c r="B123" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B123" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C123" s="9" t="n">
         <v>0.121159919609532</v>
@@ -4100,8 +4150,10 @@
           <t>003</t>
         </is>
       </c>
-      <c r="I123" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="I123" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J123" s="9" t="n">
         <v>0.128583733234896</v>
@@ -4122,8 +4174,10 @@
           <t>004</t>
         </is>
       </c>
-      <c r="B124" s="9" t="n">
-        <v>0.09999507807405038</v>
+      <c r="B124" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C124" s="9" t="n">
         <v>0.1508882565561794</v>
@@ -4142,8 +4196,10 @@
           <t>004</t>
         </is>
       </c>
-      <c r="I124" s="9" t="n">
-        <v>0.09999507807405038</v>
+      <c r="I124" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J124" s="9" t="n">
         <v>0.160562947012228</v>
@@ -4164,8 +4220,10 @@
           <t>005</t>
         </is>
       </c>
-      <c r="B125" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B125" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C125" s="9" t="n">
         <v>0.1857042660793168</v>
@@ -4184,8 +4242,10 @@
           <t>005</t>
         </is>
       </c>
-      <c r="I125" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="I125" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J125" s="9" t="n">
         <v>0.1948713531604917</v>
@@ -4206,8 +4266,10 @@
           <t>006</t>
         </is>
       </c>
-      <c r="B126" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B126" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C126" s="9" t="n">
         <v>0.2246957128062098</v>
@@ -4226,8 +4288,10 @@
           <t>006</t>
         </is>
       </c>
-      <c r="I126" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="I126" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J126" s="9" t="n">
         <v>0.2336474472688494</v>
@@ -4248,8 +4312,10 @@
           <t>007</t>
         </is>
       </c>
-      <c r="B127" s="9" t="n">
-        <v>0.09999507807405038</v>
+      <c r="B127" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C127" s="9" t="n">
         <v>0.2688088876388693</v>
@@ -4268,8 +4334,10 @@
           <t>007</t>
         </is>
       </c>
-      <c r="I127" s="9" t="n">
-        <v>0.09999507807405038</v>
+      <c r="I127" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J127" s="9" t="n">
         <v>0.2751459007171987</v>
@@ -4290,8 +4358,10 @@
           <t>008</t>
         </is>
       </c>
-      <c r="B128" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B128" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C128" s="9" t="n">
         <v>0.3160347612089518</v>
@@ -4310,8 +4380,10 @@
           <t>008</t>
         </is>
       </c>
-      <c r="I128" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="I128" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J128" s="9" t="n">
         <v>0.320995154964239</v>
@@ -4332,8 +4404,10 @@
           <t>009</t>
         </is>
       </c>
-      <c r="B129" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B129" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C129" s="9" t="n">
         <v>0.3681468923463947</v>
@@ -4352,8 +4426,10 @@
           <t>009</t>
         </is>
       </c>
-      <c r="I129" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="I129" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J129" s="9" t="n">
         <v>0.3703549260342895</v>
@@ -4374,8 +4450,10 @@
           <t>010</t>
         </is>
       </c>
-      <c r="B130" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B130" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C130" s="9" t="n">
         <v>0.4240362253749893</v>
@@ -4394,8 +4472,10 @@
           <t>010</t>
         </is>
       </c>
-      <c r="I130" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="I130" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J130" s="9" t="n">
         <v>0.4240362253749893</v>
@@ -4430,7 +4510,7 @@
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>本轮模型</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="B135" s="5" t="n"/>
@@ -4517,8 +4597,10 @@
           <t>001</t>
         </is>
       </c>
-      <c r="B137" s="9" t="n">
-        <v>0.1000015280940083</v>
+      <c r="B137" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C137" s="9" t="n">
         <v>0.0009779652211118243</v>
@@ -4537,8 +4619,10 @@
           <t>001</t>
         </is>
       </c>
-      <c r="I137" s="9" t="n">
-        <v>0.1000015280940083</v>
+      <c r="I137" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J137" s="9" t="n">
         <v>0.0006417896763546347</v>
@@ -4559,8 +4643,10 @@
           <t>002</t>
         </is>
       </c>
-      <c r="B138" s="9" t="n">
-        <v>0.09999847190599166</v>
+      <c r="B138" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C138" s="9" t="n">
         <v>0.001344722727342186</v>
@@ -4579,8 +4665,10 @@
           <t>002</t>
         </is>
       </c>
-      <c r="I138" s="9" t="n">
-        <v>0.09999847190599166</v>
+      <c r="I138" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J138" s="9" t="n">
         <v>0.0008557326446723002</v>
@@ -4601,8 +4689,10 @@
           <t>003</t>
         </is>
       </c>
-      <c r="B139" s="9" t="n">
-        <v>0.1000015280940083</v>
+      <c r="B139" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C139" s="9" t="n">
         <v>0.001752205537784479</v>
@@ -4621,8 +4711,10 @@
           <t>003</t>
         </is>
       </c>
-      <c r="I139" s="9" t="n">
-        <v>0.1000015280940083</v>
+      <c r="I139" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J139" s="9" t="n">
         <v>0.001151158289358407</v>
@@ -4643,8 +4735,10 @@
           <t>004</t>
         </is>
       </c>
-      <c r="B140" s="9" t="n">
-        <v>0.09999847190599166</v>
+      <c r="B140" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C140" s="9" t="n">
         <v>0.002154612551764184</v>
@@ -4663,8 +4757,10 @@
           <t>004</t>
         </is>
       </c>
-      <c r="I140" s="9" t="n">
-        <v>0.09999847190599166</v>
+      <c r="I140" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J140" s="9" t="n">
         <v>0.001596858238718846</v>
@@ -4685,8 +4781,10 @@
           <t>005</t>
         </is>
       </c>
-      <c r="B141" s="9" t="n">
-        <v>0.1000015280940083</v>
+      <c r="B141" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C141" s="9" t="n">
         <v>0.00263442601908278</v>
@@ -4705,8 +4803,10 @@
           <t>005</t>
         </is>
       </c>
-      <c r="I141" s="9" t="n">
-        <v>0.1000015280940083</v>
+      <c r="I141" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J141" s="9" t="n">
         <v>0.002182111574971119</v>
@@ -4727,8 +4827,10 @@
           <t>006</t>
         </is>
       </c>
-      <c r="B142" s="9" t="n">
-        <v>0.09999847190599166</v>
+      <c r="B142" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C142" s="9" t="n">
         <v>0.003295589411327252</v>
@@ -4747,8 +4849,10 @@
           <t>006</t>
         </is>
       </c>
-      <c r="I142" s="9" t="n">
-        <v>0.09999847190599166</v>
+      <c r="I142" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J142" s="9" t="n">
         <v>0.002888097675769013</v>
@@ -4769,8 +4873,10 @@
           <t>007</t>
         </is>
       </c>
-      <c r="B143" s="9" t="n">
-        <v>0.09999847190599166</v>
+      <c r="B143" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C143" s="9" t="n">
         <v>0.004112764852014688</v>
@@ -4789,8 +4895,10 @@
           <t>007</t>
         </is>
       </c>
-      <c r="I143" s="9" t="n">
-        <v>0.09999847190599166</v>
+      <c r="I143" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J143" s="9" t="n">
         <v>0.003942491147950385</v>
@@ -4811,8 +4919,10 @@
           <t>008</t>
         </is>
       </c>
-      <c r="B144" s="9" t="n">
-        <v>0.1000015280940083</v>
+      <c r="B144" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C144" s="9" t="n">
         <v>0.00561574548066197</v>
@@ -4831,8 +4941,10 @@
           <t>008</t>
         </is>
       </c>
-      <c r="I144" s="9" t="n">
-        <v>0.1000015280940083</v>
+      <c r="I144" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J144" s="9" t="n">
         <v>0.005573722895432527</v>
@@ -4853,8 +4965,10 @@
           <t>009</t>
         </is>
       </c>
-      <c r="B145" s="9" t="n">
-        <v>0.09999847190599166</v>
+      <c r="B145" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C145" s="9" t="n">
         <v>0.008530174814251369</v>
@@ -4873,8 +4987,10 @@
           <t>009</t>
         </is>
       </c>
-      <c r="I145" s="9" t="n">
-        <v>0.09999847190599166</v>
+      <c r="I145" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J145" s="9" t="n">
         <v>0.008845981445511471</v>
@@ -4895,8 +5011,10 @@
           <t>010</t>
         </is>
       </c>
-      <c r="B146" s="9" t="n">
-        <v>0.1000015280940083</v>
+      <c r="B146" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C146" s="9" t="n">
         <v>0.02395134548677435</v>
@@ -4915,8 +5033,10 @@
           <t>010</t>
         </is>
       </c>
-      <c r="I146" s="9" t="n">
-        <v>0.1000015280940083</v>
+      <c r="I146" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J146" s="9" t="n">
         <v>0.02395134548677435</v>
@@ -5679,12 +5799,12 @@
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>本轮 PSI</t>
+          <t>G卡V7 PSI</t>
         </is>
       </c>
       <c r="C188" s="6" t="inlineStr">
         <is>
-          <t>本轮样本数</t>
+          <t>G卡V7 样本数</t>
         </is>
       </c>
       <c r="D188" s="6" t="inlineStr">
@@ -5694,7 +5814,7 @@
       </c>
       <c r="E188" s="6" t="inlineStr">
         <is>
-          <t>G卡V6样本数</t>
+          <t>G卡V6 样本数</t>
         </is>
       </c>
     </row>
@@ -5893,7 +6013,7 @@
     <row r="201">
       <c r="A201" s="7" t="inlineStr">
         <is>
-          <t>本轮</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="B201" s="7" t="n">
@@ -5912,7 +6032,7 @@
     <row r="202">
       <c r="A202" s="7" t="inlineStr">
         <is>
-          <t>本轮</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="B202" s="7" t="n">
@@ -5931,7 +6051,7 @@
     <row r="203">
       <c r="A203" s="7" t="inlineStr">
         <is>
-          <t>本轮</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="B203" s="7" t="n">
@@ -5950,7 +6070,7 @@
     <row r="204">
       <c r="A204" s="7" t="inlineStr">
         <is>
-          <t>本轮</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="B204" s="7" t="n">
@@ -5969,7 +6089,7 @@
     <row r="205">
       <c r="A205" s="7" t="inlineStr">
         <is>
-          <t>本轮</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="B205" s="7" t="n">
@@ -5988,7 +6108,7 @@
     <row r="206">
       <c r="A206" s="7" t="inlineStr">
         <is>
-          <t>本轮</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="B206" s="7" t="n">
@@ -6007,7 +6127,7 @@
     <row r="207">
       <c r="A207" s="7" t="inlineStr">
         <is>
-          <t>本轮</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="B207" s="7" t="n">
@@ -6026,7 +6146,7 @@
     <row r="208">
       <c r="A208" s="7" t="inlineStr">
         <is>
-          <t>本轮</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="B208" s="7" t="n">
@@ -6045,7 +6165,7 @@
     <row r="209">
       <c r="A209" s="7" t="inlineStr">
         <is>
-          <t>本轮</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="B209" s="7" t="n">
@@ -6064,7 +6184,7 @@
     <row r="210">
       <c r="A210" s="7" t="inlineStr">
         <is>
-          <t>本轮</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="B210" s="7" t="n">
@@ -6490,7 +6610,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
@@ -27511,7 +27631,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>最终训练特征</t>
+          <t>选取Top500特征入模</t>
         </is>
       </c>
       <c r="C10" s="7" t="n">
@@ -27860,7 +27980,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>（1）在 OOT-OOS 样本上老户次新客群上，本轮全客群模型 KS 0.440；对比G卡V5 KS 0.402 提升3.8个百分点，对比G卡V6 KS 0.436 提升0.4个百分点。</t>
+          <t>（1）在 OOT-OOS 样本上老户次新客群上，G卡V7全客群模型 KS 0.440；对比G卡V5 KS 0.402 提升3.8个百分点，对比G卡V6 KS 0.436 提升0.4个百分点。</t>
         </is>
       </c>
     </row>
@@ -27870,7 +27990,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>（2）在 OOT-OOS 样本上流失户客群上，本轮全客群模型 KS 0.652；对比G卡V5 KS 0.632 提升2.1个百分点，对比G卡V6 KS 0.651 提升0.1个百分点。</t>
+          <t>（2）在 OOT-OOS 样本上流失户客群上，G卡V7全客群模型 KS 0.652；对比G卡V5 KS 0.632 提升2.1个百分点，对比G卡V6 KS 0.651 提升0.1个百分点。</t>
         </is>
       </c>
     </row>
@@ -27880,7 +28000,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>（3）在 OOT-OOS 样本上全客群整体看，本轮模型 KS 0.718，对比G卡V5 KS 0.693 提升2.5个百分点，对比G卡V6 KS 0.716 提升0.2个百分点。</t>
+          <t>（3）在 OOT-OOS 样本上全客群整体看，G卡V7 KS 0.718，对比G卡V5 KS 0.693 提升2.5个百分点，对比G卡V6 KS 0.716 提升0.2个百分点。</t>
         </is>
       </c>
     </row>
@@ -27890,7 +28010,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>（4）当前 run 未注册老户次新/流失户专属模型得分，无法复刻历史文档中的“分客群建模 KS”对比；本摘要仅比较本轮全客群模型与已注册的 G卡V5/G卡V6 历史版本。</t>
+          <t>（4）当前 run 未注册老户次新/流失户专属模型得分，无法复刻历史文档中的“分客群建模 KS”对比；本摘要仅比较G卡V7全客群模型与已注册的 G卡V5/G卡V6 历史版本。</t>
         </is>
       </c>
     </row>
@@ -27952,7 +28072,7 @@
       <c r="A11" s="6" t="inlineStr"/>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>本轮模型</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -27978,7 +28098,7 @@
       <c r="I11" s="6" t="inlineStr"/>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>本轮模型</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
@@ -28312,7 +28432,7 @@
       <c r="A22" s="6" t="inlineStr"/>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>本轮模型</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -28338,7 +28458,7 @@
       <c r="I22" s="6" t="inlineStr"/>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>本轮模型</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="K22" s="6" t="inlineStr">
@@ -28672,7 +28792,7 @@
       <c r="A33" s="6" t="inlineStr"/>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>本轮模型</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -28698,7 +28818,7 @@
       <c r="I33" s="6" t="inlineStr"/>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>本轮模型</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
@@ -28864,7 +28984,7 @@
       <c r="A40" s="6" t="inlineStr"/>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>本轮模型</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -28890,7 +29010,7 @@
       <c r="I40" s="6" t="inlineStr"/>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>本轮模型</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="K40" s="6" t="inlineStr">
@@ -29071,7 +29191,7 @@
       <c r="A49" s="6" t="inlineStr"/>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>本轮模型</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -29097,7 +29217,7 @@
       <c r="I49" s="6" t="inlineStr"/>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>本轮模型</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="K49" s="6" t="inlineStr">
@@ -29347,7 +29467,7 @@
       <c r="A58" s="6" t="inlineStr"/>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>本轮模型</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
@@ -29373,7 +29493,7 @@
       <c r="I58" s="6" t="inlineStr"/>
       <c r="J58" s="6" t="inlineStr">
         <is>
-          <t>本轮模型</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="K58" s="6" t="inlineStr">
@@ -29623,7 +29743,7 @@
       <c r="A67" s="6" t="inlineStr"/>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>本轮模型</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
@@ -29649,7 +29769,7 @@
       <c r="I67" s="6" t="inlineStr"/>
       <c r="J67" s="6" t="inlineStr">
         <is>
-          <t>本轮模型</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="K67" s="6" t="inlineStr">
@@ -29899,7 +30019,7 @@
       <c r="A76" s="6" t="inlineStr"/>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>本轮模型</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
@@ -29925,7 +30045,7 @@
       <c r="I76" s="6" t="inlineStr"/>
       <c r="J76" s="6" t="inlineStr">
         <is>
-          <t>本轮模型</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="K76" s="6" t="inlineStr">
@@ -30175,7 +30295,7 @@
       <c r="A85" s="6" t="inlineStr"/>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>本轮模型</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
@@ -30201,7 +30321,7 @@
       <c r="I85" s="6" t="inlineStr"/>
       <c r="J85" s="6" t="inlineStr">
         <is>
-          <t>本轮模型</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="K85" s="6" t="inlineStr">
@@ -31149,13 +31269,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="15.3" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
@@ -31180,7 +31300,7 @@
     <row r="3">
       <c r="A3" s="17" t="inlineStr">
         <is>
-          <t>本轮模型</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="B3" s="5" t="n"/>
@@ -31267,8 +31387,10 @@
           <t>001</t>
         </is>
       </c>
-      <c r="B5" s="9" t="n">
-        <v>0.1000014293210929</v>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C5" s="9" t="n">
         <v>0.001184277692700357</v>
@@ -31287,8 +31409,10 @@
           <t>001</t>
         </is>
       </c>
-      <c r="I5" s="9" t="n">
-        <v>0.1000004085150885</v>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J5" s="9" t="n">
         <v>0.0009600065362147147</v>
@@ -31309,8 +31433,10 @@
           <t>002</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C6" s="9" t="n">
         <v>0.00175601588581813</v>
@@ -31329,8 +31455,10 @@
           <t>002</t>
         </is>
       </c>
-      <c r="I6" s="9" t="n">
-        <v>0.1000004085150885</v>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J6" s="9" t="n">
         <v>0.00147064831079701</v>
@@ -31351,8 +31479,10 @@
           <t>003</t>
         </is>
       </c>
-      <c r="B7" s="9" t="n">
-        <v>0.1000014293210929</v>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C7" s="9" t="n">
         <v>0.002307315346709863</v>
@@ -31371,8 +31501,10 @@
           <t>003</t>
         </is>
       </c>
-      <c r="I7" s="9" t="n">
-        <v>0.1000004085150885</v>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J7" s="9" t="n">
         <v>0.002131078339256778</v>
@@ -31393,8 +31525,10 @@
           <t>004</t>
         </is>
       </c>
-      <c r="B8" s="9" t="n">
-        <v>0.09999734554654176</v>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C8" s="9" t="n">
         <v>0.003292546593362839</v>
@@ -31413,8 +31547,10 @@
           <t>004</t>
         </is>
       </c>
-      <c r="I8" s="9" t="n">
-        <v>0.09999836593964598</v>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J8" s="9" t="n">
         <v>0.003283443377197686</v>
@@ -31435,8 +31571,10 @@
           <t>005</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n">
-        <v>0.1000014293210929</v>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C9" s="9" t="n">
         <v>0.004659577248521677</v>
@@ -31455,8 +31593,10 @@
           <t>005</t>
         </is>
       </c>
-      <c r="I9" s="9" t="n">
-        <v>0.1000004085150885</v>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J9" s="9" t="n">
         <v>0.005486357638619382</v>
@@ -31477,8 +31617,10 @@
           <t>006</t>
         </is>
       </c>
-      <c r="B10" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C10" s="9" t="n">
         <v>0.008347910129795879</v>
@@ -31497,8 +31639,10 @@
           <t>006</t>
         </is>
       </c>
-      <c r="I10" s="9" t="n">
-        <v>0.1000004085150885</v>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J10" s="9" t="n">
         <v>0.01063159793972364</v>
@@ -31519,8 +31663,10 @@
           <t>007</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C11" s="9" t="n">
         <v>0.01908581763024328</v>
@@ -31539,8 +31685,10 @@
           <t>007</t>
         </is>
       </c>
-      <c r="I11" s="9" t="n">
-        <v>0.1000004085150885</v>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J11" s="9" t="n">
         <v>0.02288557213930348</v>
@@ -31561,8 +31709,10 @@
           <t>008</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C12" s="9" t="n">
         <v>0.04262444039469721</v>
@@ -31581,8 +31731,10 @@
           <t>008</t>
         </is>
       </c>
-      <c r="I12" s="9" t="n">
-        <v>0.09999836593964598</v>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J12" s="9" t="n">
         <v>0.04786525116043936</v>
@@ -31603,8 +31755,10 @@
           <t>009</t>
         </is>
       </c>
-      <c r="B13" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C13" s="9" t="n">
         <v>0.08662607085813852</v>
@@ -31623,8 +31777,10 @@
           <t>009</t>
         </is>
       </c>
-      <c r="I13" s="9" t="n">
-        <v>0.1000004085150885</v>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J13" s="9" t="n">
         <v>0.09172075711497435</v>
@@ -31645,8 +31801,10 @@
           <t>010</t>
         </is>
       </c>
-      <c r="B14" s="9" t="n">
-        <v>0.1000014293210929</v>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C14" s="9" t="n">
         <v>0.1567332253855594</v>
@@ -31665,8 +31823,10 @@
           <t>010</t>
         </is>
       </c>
-      <c r="I14" s="9" t="n">
-        <v>0.1000004085150885</v>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J14" s="9" t="n">
         <v>0.1566205997818529</v>
@@ -31773,8 +31933,10 @@
           <t>001</t>
         </is>
       </c>
-      <c r="B19" s="9" t="n">
-        <v>0.1335051272731728</v>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>13.4%</t>
+        </is>
       </c>
       <c r="C19" s="9" t="n">
         <v>0.00541433422042764</v>
@@ -31793,8 +31955,10 @@
           <t>001</t>
         </is>
       </c>
-      <c r="I19" s="9" t="n">
-        <v>0.1010019540861227</v>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>10.1%</t>
+        </is>
       </c>
       <c r="J19" s="9" t="n">
         <v>0.000849085211765895</v>
@@ -31815,8 +31979,10 @@
           <t>002</t>
         </is>
       </c>
-      <c r="B20" s="9" t="n">
-        <v>0.06672806053898647</v>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>6.7%</t>
+        </is>
       </c>
       <c r="C20" s="9" t="n">
         <v>0.006699911279713647</v>
@@ -31835,8 +32001,10 @@
           <t>002</t>
         </is>
       </c>
-      <c r="I20" s="9" t="n">
-        <v>0.09932556463287888</v>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>9.9%</t>
+        </is>
       </c>
       <c r="J20" s="9" t="n">
         <v>0.001396406038182022</v>
@@ -31857,8 +32025,10 @@
           <t>003</t>
         </is>
       </c>
-      <c r="B21" s="9" t="n">
-        <v>0.09979499075008065</v>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C21" s="9" t="n">
         <v>0.006370207031728531</v>
@@ -31877,8 +32047,10 @@
           <t>003</t>
         </is>
       </c>
-      <c r="I21" s="9" t="n">
-        <v>0.09967268546972596</v>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J21" s="9" t="n">
         <v>0.002021467026946088</v>
@@ -31899,8 +32071,10 @@
           <t>004</t>
         </is>
       </c>
-      <c r="B22" s="9" t="n">
-        <v>0.1002462561308792</v>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C22" s="9" t="n">
         <v>0.007050013263411349</v>
@@ -31919,8 +32093,10 @@
           <t>004</t>
         </is>
       </c>
-      <c r="I22" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J22" s="9" t="n">
         <v>0.003149614338147087</v>
@@ -31941,8 +32117,10 @@
           <t>005</t>
         </is>
       </c>
-      <c r="B23" s="9" t="n">
-        <v>0.09984808079488049</v>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C23" s="9" t="n">
         <v>0.007757413433390357</v>
@@ -31961,8 +32139,10 @@
           <t>005</t>
         </is>
       </c>
-      <c r="I23" s="9" t="n">
-        <v>0.1000014293210929</v>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J23" s="9" t="n">
         <v>0.005447744127544186</v>
@@ -31983,8 +32163,10 @@
           <t>006</t>
         </is>
       </c>
-      <c r="B24" s="9" t="n">
-        <v>0.0998766677420804</v>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C24" s="9" t="n">
         <v>0.01292880479172339</v>
@@ -32003,8 +32185,10 @@
           <t>006</t>
         </is>
       </c>
-      <c r="I24" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J24" s="9" t="n">
         <v>0.01130864466421187</v>
@@ -32025,8 +32209,10 @@
           <t>007</t>
         </is>
       </c>
-      <c r="B25" s="9" t="n">
-        <v>0.10000122515488</v>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C25" s="9" t="n">
         <v>0.02473644600278868</v>
@@ -32045,8 +32231,10 @@
           <t>007</t>
         </is>
       </c>
-      <c r="I25" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J25" s="9" t="n">
         <v>0.02362464266962254</v>
@@ -32067,8 +32255,10 @@
           <t>008</t>
         </is>
       </c>
-      <c r="B26" s="9" t="n">
-        <v>0.09999918323008</v>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C26" s="9" t="n">
         <v>0.04778616952578825</v>
@@ -32087,8 +32277,10 @@
           <t>008</t>
         </is>
       </c>
-      <c r="I26" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J26" s="9" t="n">
         <v>0.04919932413462177</v>
@@ -32109,8 +32301,10 @@
           <t>009</t>
         </is>
       </c>
-      <c r="B27" s="9" t="n">
-        <v>0.09999918323008</v>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C27" s="9" t="n">
         <v>0.08969960976495145</v>
@@ -32129,8 +32323,10 @@
           <t>009</t>
         </is>
       </c>
-      <c r="I27" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J27" s="9" t="n">
         <v>0.09280619282706548</v>
@@ -32151,8 +32347,10 @@
           <t>010</t>
         </is>
       </c>
-      <c r="B28" s="9" t="n">
-        <v>0.10000122515488</v>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C28" s="9" t="n">
         <v>0.1567361057226984</v>
@@ -32171,8 +32369,10 @@
           <t>010</t>
         </is>
       </c>
-      <c r="I28" s="9" t="n">
-        <v>0.1000014293210929</v>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J28" s="9" t="n">
         <v>0.1567332253855594</v>
@@ -32239,8 +32439,10 @@
           <t>001</t>
         </is>
       </c>
-      <c r="B33" s="9" t="n">
-        <v>0.1000014293210929</v>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C33" s="9" t="n">
         <v>0.0007146503318019398</v>
@@ -32261,8 +32463,10 @@
           <t>002</t>
         </is>
       </c>
-      <c r="B34" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C34" s="9" t="n">
         <v>0.001143452204718782</v>
@@ -32283,8 +32487,10 @@
           <t>003</t>
         </is>
       </c>
-      <c r="B35" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C35" s="9" t="n">
         <v>0.001912566446369867</v>
@@ -32305,8 +32511,10 @@
           <t>004</t>
         </is>
       </c>
-      <c r="B36" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C36" s="9" t="n">
         <v>0.002863749827715585</v>
@@ -32327,8 +32535,10 @@
           <t>005</t>
         </is>
       </c>
-      <c r="B37" s="9" t="n">
-        <v>0.1000014293210929</v>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C37" s="9" t="n">
         <v>0.004630990885033813</v>
@@ -32349,8 +32559,10 @@
           <t>006</t>
         </is>
       </c>
-      <c r="B38" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C38" s="9" t="n">
         <v>0.008698433873525589</v>
@@ -32371,8 +32583,10 @@
           <t>007</t>
         </is>
       </c>
-      <c r="B39" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C39" s="9" t="n">
         <v>0.01999883320693075</v>
@@ -32393,8 +32607,10 @@
           <t>008</t>
         </is>
       </c>
-      <c r="B40" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C40" s="9" t="n">
         <v>0.04469185337192504</v>
@@ -32415,8 +32631,10 @@
           <t>009</t>
         </is>
       </c>
-      <c r="B41" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C41" s="9" t="n">
         <v>0.0883344525918397</v>
@@ -32437,8 +32655,10 @@
           <t>010</t>
         </is>
       </c>
-      <c r="B42" s="9" t="n">
-        <v>0.1000014293210929</v>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C42" s="9" t="n">
         <v>0.1567332253855594</v>
@@ -32474,7 +32694,7 @@
     <row r="48">
       <c r="A48" s="17" t="inlineStr">
         <is>
-          <t>本轮模型</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="B48" s="5" t="n"/>
@@ -32561,8 +32781,10 @@
           <t>001</t>
         </is>
       </c>
-      <c r="B50" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C50" s="9" t="n">
         <v>0.06459948320413436</v>
@@ -32581,8 +32803,10 @@
           <t>001</t>
         </is>
       </c>
-      <c r="I50" s="9" t="n">
-        <v>0.1000049266544321</v>
+      <c r="I50" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J50" s="9" t="n">
         <v>0.08892173163372129</v>
@@ -32603,8 +32827,10 @@
           <t>002</t>
         </is>
       </c>
-      <c r="B51" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C51" s="9" t="n">
         <v>0.09246954595791805</v>
@@ -32623,8 +32849,10 @@
           <t>002</t>
         </is>
       </c>
-      <c r="I51" s="9" t="n">
-        <v>0.09999876833639196</v>
+      <c r="I51" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J51" s="9" t="n">
         <v>0.1166363888290175</v>
@@ -32645,8 +32873,10 @@
           <t>003</t>
         </is>
       </c>
-      <c r="B52" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C52" s="9" t="n">
         <v>0.121159919609532</v>
@@ -32665,8 +32895,10 @@
           <t>003</t>
         </is>
       </c>
-      <c r="I52" s="9" t="n">
-        <v>0.09999876833639196</v>
+      <c r="I52" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J52" s="9" t="n">
         <v>0.1446987580827261</v>
@@ -32687,8 +32919,10 @@
           <t>004</t>
         </is>
       </c>
-      <c r="B53" s="9" t="n">
-        <v>0.09999507807405038</v>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C53" s="9" t="n">
         <v>0.1508882565561794</v>
@@ -32707,8 +32941,10 @@
           <t>004</t>
         </is>
       </c>
-      <c r="I53" s="9" t="n">
-        <v>0.09999876833639196</v>
+      <c r="I53" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J53" s="9" t="n">
         <v>0.1751574215201761</v>
@@ -32729,8 +32965,10 @@
           <t>005</t>
         </is>
       </c>
-      <c r="B54" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C54" s="9" t="n">
         <v>0.1857042660793168</v>
@@ -32749,8 +32987,10 @@
           <t>005</t>
         </is>
       </c>
-      <c r="I54" s="9" t="n">
-        <v>0.09999876833639196</v>
+      <c r="I54" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J54" s="9" t="n">
         <v>0.2097892623566651</v>
@@ -32771,8 +33011,10 @@
           <t>006</t>
         </is>
       </c>
-      <c r="B55" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C55" s="9" t="n">
         <v>0.2246957128062098</v>
@@ -32791,8 +33033,10 @@
           <t>006</t>
         </is>
       </c>
-      <c r="I55" s="9" t="n">
-        <v>0.09999876833639196</v>
+      <c r="I55" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J55" s="9" t="n">
         <v>0.247339087951226</v>
@@ -32813,8 +33057,10 @@
           <t>007</t>
         </is>
       </c>
-      <c r="B56" s="9" t="n">
-        <v>0.09999507807405038</v>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C56" s="9" t="n">
         <v>0.2688088876388693</v>
@@ -32833,8 +33079,10 @@
           <t>007</t>
         </is>
       </c>
-      <c r="I56" s="9" t="n">
-        <v>0.09999876833639196</v>
+      <c r="I56" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J56" s="9" t="n">
         <v>0.2875944645323621</v>
@@ -32855,8 +33103,10 @@
           <t>008</t>
         </is>
       </c>
-      <c r="B57" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C57" s="9" t="n">
         <v>0.3160347612089518</v>
@@ -32875,8 +33125,10 @@
           <t>008</t>
         </is>
       </c>
-      <c r="I57" s="9" t="n">
-        <v>0.09999876833639196</v>
+      <c r="I57" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J57" s="9" t="n">
         <v>0.3294946306916593</v>
@@ -32897,8 +33149,10 @@
           <t>009</t>
         </is>
       </c>
-      <c r="B58" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C58" s="9" t="n">
         <v>0.3681468923463947</v>
@@ -32917,8 +33171,10 @@
           <t>009</t>
         </is>
       </c>
-      <c r="I58" s="9" t="n">
-        <v>0.09999876833639196</v>
+      <c r="I58" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J58" s="9" t="n">
         <v>0.3741951376391616</v>
@@ -32939,8 +33195,10 @@
           <t>010</t>
         </is>
       </c>
-      <c r="B59" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C59" s="9" t="n">
         <v>0.4240362253749893</v>
@@ -32959,8 +33217,10 @@
           <t>010</t>
         </is>
       </c>
-      <c r="I59" s="9" t="n">
-        <v>0.1000049266544321</v>
+      <c r="I59" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J59" s="9" t="n">
         <v>0.4239447722038157</v>
@@ -33067,8 +33327,10 @@
           <t>001</t>
         </is>
       </c>
-      <c r="B64" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B64" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C64" s="9" t="n">
         <v>0.1040974529346622</v>
@@ -33087,8 +33349,10 @@
           <t>001</t>
         </is>
       </c>
-      <c r="I64" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="I64" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J64" s="9" t="n">
         <v>0.09326934908330257</v>
@@ -33109,8 +33373,10 @@
           <t>002</t>
         </is>
       </c>
-      <c r="B65" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B65" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C65" s="9" t="n">
         <v>0.1237233911652516</v>
@@ -33129,8 +33395,10 @@
           <t>002</t>
         </is>
       </c>
-      <c r="I65" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="I65" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J65" s="9" t="n">
         <v>0.1230773963332103</v>
@@ -33151,8 +33419,10 @@
           <t>003</t>
         </is>
       </c>
-      <c r="B66" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B66" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C66" s="9" t="n">
         <v>0.1465280341249333</v>
@@ -33171,8 +33441,10 @@
           <t>003</t>
         </is>
       </c>
-      <c r="I66" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="I66" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J66" s="9" t="n">
         <v>0.1526598580862147</v>
@@ -33193,8 +33465,10 @@
           <t>004</t>
         </is>
       </c>
-      <c r="B67" s="9" t="n">
-        <v>0.09999507807405038</v>
+      <c r="B67" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C67" s="9" t="n">
         <v>0.1744059063293086</v>
@@ -33213,8 +33487,10 @@
           <t>004</t>
         </is>
       </c>
-      <c r="I67" s="9" t="n">
-        <v>0.09999507807405038</v>
+      <c r="I67" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J67" s="9" t="n">
         <v>0.1835884026763055</v>
@@ -33235,8 +33511,10 @@
           <t>005</t>
         </is>
       </c>
-      <c r="B68" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C68" s="9" t="n">
         <v>0.2041614883904072</v>
@@ -33255,8 +33533,10 @@
           <t>005</t>
         </is>
       </c>
-      <c r="I68" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="I68" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J68" s="9" t="n">
         <v>0.2171676777122888</v>
@@ -33277,8 +33557,10 @@
           <t>006</t>
         </is>
       </c>
-      <c r="B69" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B69" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C69" s="9" t="n">
         <v>0.2397383181403361</v>
@@ -33297,8 +33579,10 @@
           <t>006</t>
         </is>
       </c>
-      <c r="I69" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="I69" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J69" s="9" t="n">
         <v>0.2531813008213447</v>
@@ -33319,8 +33603,10 @@
           <t>007</t>
         </is>
       </c>
-      <c r="B70" s="9" t="n">
-        <v>0.09999507807405038</v>
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C70" s="9" t="n">
         <v>0.2798920686260723</v>
@@ -33339,8 +33625,10 @@
           <t>007</t>
         </is>
       </c>
-      <c r="I70" s="9" t="n">
-        <v>0.09999507807405038</v>
+      <c r="I70" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J70" s="9" t="n">
         <v>0.2920211643931936</v>
@@ -33361,8 +33649,10 @@
           <t>008</t>
         </is>
       </c>
-      <c r="B71" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C71" s="9" t="n">
         <v>0.3237483657617473</v>
@@ -33381,8 +33671,10 @@
           <t>008</t>
         </is>
       </c>
-      <c r="I71" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="I71" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J71" s="9" t="n">
         <v>0.3341998000461432</v>
@@ -33403,8 +33695,10 @@
           <t>009</t>
         </is>
       </c>
-      <c r="B72" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C72" s="9" t="n">
         <v>0.372125454595171</v>
@@ -33423,8 +33717,10 @@
           <t>009</t>
         </is>
       </c>
-      <c r="I72" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="I72" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J72" s="9" t="n">
         <v>0.3770884033797271</v>
@@ -33445,8 +33741,10 @@
           <t>010</t>
         </is>
       </c>
-      <c r="B73" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C73" s="9" t="n">
         <v>0.4240362253749893</v>
@@ -33465,8 +33763,10 @@
           <t>010</t>
         </is>
       </c>
-      <c r="I73" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="I73" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J73" s="9" t="n">
         <v>0.4240362253749893</v>
@@ -33533,8 +33833,10 @@
           <t>001</t>
         </is>
       </c>
-      <c r="B78" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B78" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C78" s="9" t="n">
         <v>0.06921373200442968</v>
@@ -33555,8 +33857,10 @@
           <t>002</t>
         </is>
       </c>
-      <c r="B79" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B79" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C79" s="9" t="n">
         <v>0.09972929740371601</v>
@@ -33577,8 +33881,10 @@
           <t>003</t>
         </is>
       </c>
-      <c r="B80" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B80" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C80" s="9" t="n">
         <v>0.128583733234896</v>
@@ -33599,8 +33905,10 @@
           <t>004</t>
         </is>
       </c>
-      <c r="B81" s="9" t="n">
-        <v>0.09999507807405038</v>
+      <c r="B81" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C81" s="9" t="n">
         <v>0.160562947012228</v>
@@ -33621,8 +33929,10 @@
           <t>005</t>
         </is>
       </c>
-      <c r="B82" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B82" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C82" s="9" t="n">
         <v>0.1948713531604917</v>
@@ -33643,8 +33953,10 @@
           <t>006</t>
         </is>
       </c>
-      <c r="B83" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B83" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C83" s="9" t="n">
         <v>0.2336474472688494</v>
@@ -33665,8 +33977,10 @@
           <t>007</t>
         </is>
       </c>
-      <c r="B84" s="9" t="n">
-        <v>0.09999507807405038</v>
+      <c r="B84" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C84" s="9" t="n">
         <v>0.2751459007171987</v>
@@ -33687,8 +34001,10 @@
           <t>008</t>
         </is>
       </c>
-      <c r="B85" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B85" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C85" s="9" t="n">
         <v>0.320995154964239</v>
@@ -33709,8 +34025,10 @@
           <t>009</t>
         </is>
       </c>
-      <c r="B86" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B86" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C86" s="9" t="n">
         <v>0.3703549260342895</v>
@@ -33731,8 +34049,10 @@
           <t>010</t>
         </is>
       </c>
-      <c r="B87" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B87" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C87" s="9" t="n">
         <v>0.4240362253749893</v>
@@ -33768,7 +34088,7 @@
     <row r="93">
       <c r="A93" s="17" t="inlineStr">
         <is>
-          <t>本轮模型</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="B93" s="5" t="n"/>
@@ -33855,8 +34175,10 @@
           <t>001</t>
         </is>
       </c>
-      <c r="B95" s="9" t="n">
-        <v>0.1000015280940083</v>
+      <c r="B95" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C95" s="9" t="n">
         <v>0.0009779652211118243</v>
@@ -33875,8 +34197,10 @@
           <t>001</t>
         </is>
       </c>
-      <c r="I95" s="9" t="n">
-        <v>0.1000012225088326</v>
+      <c r="I95" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J95" s="9" t="n">
         <v>0.0007334963325183374</v>
@@ -33897,8 +34221,10 @@
           <t>002</t>
         </is>
       </c>
-      <c r="B96" s="9" t="n">
-        <v>0.09999847190599166</v>
+      <c r="B96" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C96" s="9" t="n">
         <v>0.001344722727342186</v>
@@ -33917,8 +34243,10 @@
           <t>002</t>
         </is>
       </c>
-      <c r="I96" s="9" t="n">
-        <v>0.1000012225088326</v>
+      <c r="I96" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J96" s="9" t="n">
         <v>0.001115525672371638</v>
@@ -33939,8 +34267,10 @@
           <t>003</t>
         </is>
       </c>
-      <c r="B97" s="9" t="n">
-        <v>0.1000015280940083</v>
+      <c r="B97" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C97" s="9" t="n">
         <v>0.001752205537784479</v>
@@ -33959,8 +34289,10 @@
           <t>003</t>
         </is>
       </c>
-      <c r="I97" s="9" t="n">
-        <v>0.09999816623675106</v>
+      <c r="I97" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J97" s="9" t="n">
         <v>0.001467007610101977</v>
@@ -33981,8 +34313,10 @@
           <t>004</t>
         </is>
       </c>
-      <c r="B98" s="9" t="n">
-        <v>0.09999847190599166</v>
+      <c r="B98" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C98" s="9" t="n">
         <v>0.002154612551764184</v>
@@ -34001,8 +34335,10 @@
           <t>004</t>
         </is>
       </c>
-      <c r="I98" s="9" t="n">
-        <v>0.1000012225088326</v>
+      <c r="I98" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J98" s="9" t="n">
         <v>0.001871958068139274</v>
@@ -34023,8 +34359,10 @@
           <t>005</t>
         </is>
       </c>
-      <c r="B99" s="9" t="n">
-        <v>0.1000015280940083</v>
+      <c r="B99" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C99" s="9" t="n">
         <v>0.00263442601908278</v>
@@ -34043,8 +34381,10 @@
           <t>005</t>
         </is>
       </c>
-      <c r="I99" s="9" t="n">
-        <v>0.09999816623675106</v>
+      <c r="I99" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J99" s="9" t="n">
         <v>0.002506143106883947</v>
@@ -34065,8 +34405,10 @@
           <t>006</t>
         </is>
       </c>
-      <c r="B100" s="9" t="n">
-        <v>0.09999847190599166</v>
+      <c r="B100" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C100" s="9" t="n">
         <v>0.003295589411327252</v>
@@ -34085,8 +34427,10 @@
           <t>006</t>
         </is>
       </c>
-      <c r="I100" s="9" t="n">
-        <v>0.1000012225088326</v>
+      <c r="I100" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J100" s="9" t="n">
         <v>0.003285485793457553</v>
@@ -34107,8 +34451,10 @@
           <t>007</t>
         </is>
       </c>
-      <c r="B101" s="9" t="n">
-        <v>0.09999847190599166</v>
+      <c r="B101" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C101" s="9" t="n">
         <v>0.004112764852014688</v>
@@ -34127,8 +34473,10 @@
           <t>007</t>
         </is>
       </c>
-      <c r="I101" s="9" t="n">
-        <v>0.09999816623675106</v>
+      <c r="I101" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J101" s="9" t="n">
         <v>0.004601876552696726</v>
@@ -34149,8 +34497,10 @@
           <t>008</t>
         </is>
       </c>
-      <c r="B102" s="9" t="n">
-        <v>0.1000015280940083</v>
+      <c r="B102" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C102" s="9" t="n">
         <v>0.00561574548066197</v>
@@ -34169,8 +34519,10 @@
           <t>008</t>
         </is>
       </c>
-      <c r="I102" s="9" t="n">
-        <v>0.1000012225088326</v>
+      <c r="I102" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J102" s="9" t="n">
         <v>0.006655027372715916</v>
@@ -34191,8 +34543,10 @@
           <t>009</t>
         </is>
       </c>
-      <c r="B103" s="9" t="n">
-        <v>0.09999847190599166</v>
+      <c r="B103" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C103" s="9" t="n">
         <v>0.008530174814251369</v>
@@ -34211,8 +34565,10 @@
           <t>009</t>
         </is>
       </c>
-      <c r="I103" s="9" t="n">
-        <v>0.09999816623675106</v>
+      <c r="I103" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J103" s="9" t="n">
         <v>0.01023512951819503</v>
@@ -34233,8 +34589,10 @@
           <t>010</t>
         </is>
       </c>
-      <c r="B104" s="9" t="n">
-        <v>0.1000015280940083</v>
+      <c r="B104" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C104" s="9" t="n">
         <v>0.02395134548677435</v>
@@ -34253,8 +34611,10 @@
           <t>010</t>
         </is>
       </c>
-      <c r="I104" s="9" t="n">
-        <v>0.1000012225088326</v>
+      <c r="I104" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J104" s="9" t="n">
         <v>0.02395200430323109</v>
@@ -34361,8 +34721,10 @@
           <t>001</t>
         </is>
       </c>
-      <c r="B109" s="9" t="n">
-        <v>0.1996845927211824</v>
+      <c r="B109" s="9" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
       </c>
       <c r="C109" s="9" t="n">
         <v>0.005418146198114363</v>
@@ -34381,8 +34743,10 @@
           <t>001</t>
         </is>
       </c>
-      <c r="I109" s="9" t="n">
-        <v>0.1042251799330695</v>
+      <c r="I109" s="9" t="inlineStr">
+        <is>
+          <t>10.4%</t>
+        </is>
       </c>
       <c r="J109" s="9" t="n">
         <v>0.0006157816027915433</v>
@@ -34403,8 +34767,10 @@
           <t>002</t>
         </is>
       </c>
-      <c r="B110" s="9" t="n">
-        <v>0.0003300773848091052</v>
+      <c r="B110" s="9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
       </c>
       <c r="C110" s="9" t="n">
         <v>0.005424485055925677</v>
@@ -34423,8 +34789,10 @@
           <t>002</t>
         </is>
       </c>
-      <c r="I110" s="9" t="n">
-        <v>0.09579315719503063</v>
+      <c r="I110" s="9" t="inlineStr">
+        <is>
+          <t>9.6%</t>
+        </is>
       </c>
       <c r="J110" s="9" t="n">
         <v>0.001054288202667807</v>
@@ -34445,8 +34813,10 @@
           <t>003</t>
         </is>
       </c>
-      <c r="B111" s="9" t="n">
-        <v>0.1000042787809142</v>
+      <c r="B111" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C111" s="9" t="n">
         <v>0.006703000050934651</v>
@@ -34465,8 +34835,10 @@
           <t>003</t>
         </is>
       </c>
-      <c r="I111" s="9" t="n">
-        <v>0.09998624715392491</v>
+      <c r="I111" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J111" s="9" t="n">
         <v>0.001395637867628332</v>
@@ -34487,8 +34859,10 @@
           <t>004</t>
         </is>
       </c>
-      <c r="B112" s="9" t="n">
-        <v>0.1037420995366692</v>
+      <c r="B112" s="9" t="inlineStr">
+        <is>
+          <t>10.4%</t>
+        </is>
       </c>
       <c r="C112" s="9" t="n">
         <v>0.006161578696379504</v>
@@ -34507,8 +34881,10 @@
           <t>004</t>
         </is>
       </c>
-      <c r="I112" s="9" t="n">
-        <v>0.09999541571797498</v>
+      <c r="I112" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J112" s="9" t="n">
         <v>0.001764948579636619</v>
@@ -34529,8 +34905,10 @@
           <t>005</t>
         </is>
       </c>
-      <c r="B113" s="9" t="n">
-        <v>0.09805132092079365</v>
+      <c r="B113" s="9" t="inlineStr">
+        <is>
+          <t>9.8%</t>
+        </is>
       </c>
       <c r="C113" s="9" t="n">
         <v>0.006790871606848122</v>
@@ -34549,8 +34927,10 @@
           <t>005</t>
         </is>
       </c>
-      <c r="I113" s="9" t="n">
-        <v>0.1000015280940083</v>
+      <c r="I113" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J113" s="9" t="n">
         <v>0.002432718226438391</v>
@@ -34571,8 +34951,10 @@
           <t>006</t>
         </is>
       </c>
-      <c r="B114" s="9" t="n">
-        <v>0.09818885316446412</v>
+      <c r="B114" s="9" t="inlineStr">
+        <is>
+          <t>9.8%</t>
+        </is>
       </c>
       <c r="C114" s="9" t="n">
         <v>0.007095630558583523</v>
@@ -34591,8 +34973,10 @@
           <t>006</t>
         </is>
       </c>
-      <c r="I114" s="9" t="n">
-        <v>0.09999847190599166</v>
+      <c r="I114" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J114" s="9" t="n">
         <v>0.003071468956770221</v>
@@ -34613,8 +34997,10 @@
           <t>007</t>
         </is>
       </c>
-      <c r="B115" s="9" t="n">
-        <v>0.1000073350529958</v>
+      <c r="B115" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C115" s="9" t="n">
         <v>0.007326231225986727</v>
@@ -34633,8 +35019,10 @@
           <t>007</t>
         </is>
       </c>
-      <c r="I115" s="9" t="n">
-        <v>0.09999847190599166</v>
+      <c r="I115" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J115" s="9" t="n">
         <v>0.004191352715428981</v>
@@ -34655,8 +35043,10 @@
           <t>008</t>
         </is>
       </c>
-      <c r="B116" s="9" t="n">
-        <v>0.1002365554591132</v>
+      <c r="B116" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C116" s="9" t="n">
         <v>0.008215034544392121</v>
@@ -34675,8 +35065,10 @@
           <t>008</t>
         </is>
       </c>
-      <c r="I116" s="9" t="n">
-        <v>0.1000015280940083</v>
+      <c r="I116" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J116" s="9" t="n">
         <v>0.006200241438853318</v>
@@ -34697,8 +35089,10 @@
           <t>009</t>
         </is>
       </c>
-      <c r="B117" s="9" t="n">
-        <v>0.09975366447022579</v>
+      <c r="B117" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C117" s="9" t="n">
         <v>0.01326423885138347</v>
@@ -34717,8 +35111,10 @@
           <t>009</t>
         </is>
       </c>
-      <c r="I117" s="9" t="n">
-        <v>0.09999847190599166</v>
+      <c r="I117" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J117" s="9" t="n">
         <v>0.009800192879748985</v>
@@ -34739,8 +35135,10 @@
           <t>010</t>
         </is>
       </c>
-      <c r="B118" s="9" t="n">
-        <v>0.1000012225088326</v>
+      <c r="B118" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C118" s="9" t="n">
         <v>0.02395200430323109</v>
@@ -34759,8 +35157,10 @@
           <t>010</t>
         </is>
       </c>
-      <c r="I118" s="9" t="n">
-        <v>0.1000015280940083</v>
+      <c r="I118" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J118" s="9" t="n">
         <v>0.02395134548677435</v>
@@ -34827,8 +35227,10 @@
           <t>001</t>
         </is>
       </c>
-      <c r="B123" s="9" t="n">
-        <v>0.1000015280940083</v>
+      <c r="B123" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C123" s="9" t="n">
         <v>0.0006417896763546347</v>
@@ -34849,8 +35251,10 @@
           <t>002</t>
         </is>
       </c>
-      <c r="B124" s="9" t="n">
-        <v>0.09999847190599166</v>
+      <c r="B124" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C124" s="9" t="n">
         <v>0.0008557326446723002</v>
@@ -34871,8 +35275,10 @@
           <t>003</t>
         </is>
       </c>
-      <c r="B125" s="9" t="n">
-        <v>0.1000015280940083</v>
+      <c r="B125" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C125" s="9" t="n">
         <v>0.001151158289358407</v>
@@ -34893,8 +35299,10 @@
           <t>004</t>
         </is>
       </c>
-      <c r="B126" s="9" t="n">
-        <v>0.09999847190599166</v>
+      <c r="B126" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C126" s="9" t="n">
         <v>0.001596858238718846</v>
@@ -34915,8 +35323,10 @@
           <t>005</t>
         </is>
       </c>
-      <c r="B127" s="9" t="n">
-        <v>0.1000015280940083</v>
+      <c r="B127" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C127" s="9" t="n">
         <v>0.002182111574971119</v>
@@ -34937,8 +35347,10 @@
           <t>006</t>
         </is>
       </c>
-      <c r="B128" s="9" t="n">
-        <v>0.09999847190599166</v>
+      <c r="B128" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C128" s="9" t="n">
         <v>0.002888097675769013</v>
@@ -34959,8 +35371,10 @@
           <t>007</t>
         </is>
       </c>
-      <c r="B129" s="9" t="n">
-        <v>0.09999847190599166</v>
+      <c r="B129" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C129" s="9" t="n">
         <v>0.003942491147950385</v>
@@ -34981,8 +35395,10 @@
           <t>008</t>
         </is>
       </c>
-      <c r="B130" s="9" t="n">
-        <v>0.1000015280940083</v>
+      <c r="B130" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C130" s="9" t="n">
         <v>0.005573722895432527</v>
@@ -35003,8 +35419,10 @@
           <t>009</t>
         </is>
       </c>
-      <c r="B131" s="9" t="n">
-        <v>0.09999847190599166</v>
+      <c r="B131" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C131" s="9" t="n">
         <v>0.008845981445511471</v>
@@ -35025,8 +35443,10 @@
           <t>010</t>
         </is>
       </c>
-      <c r="B132" s="9" t="n">
-        <v>0.1000015280940083</v>
+      <c r="B132" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C132" s="9" t="n">
         <v>0.02395134548677435</v>
